--- a/sources/gunjack_step4.xlsx
+++ b/sources/gunjack_step4.xlsx
@@ -1094,6 +1094,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
@@ -1131,6 +1136,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
@@ -1178,6 +1188,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
@@ -1220,6 +1235,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
@@ -1262,6 +1282,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
@@ -1297,6 +1322,11 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>251f1e2f-c3c7-4333-a3d4-49d19c52d36c</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -6037,6 +6067,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
@@ -6064,6 +6099,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
@@ -6091,6 +6131,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
@@ -6116,6 +6161,11 @@
       <c r="J119" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2fc42861-9255-4a82-8966-00993ca4d00e</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">

--- a/sources/gunjack_step4.xlsx
+++ b/sources/gunjack_step4.xlsx
@@ -5340,6 +5340,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -5447,6 +5452,11 @@
       <c r="A101" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
